--- a/Datas/TempCharacterCreateData.xlsx
+++ b/Datas/TempCharacterCreateData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="89">
   <si>
     <t>maxCharacterCount</t>
   </si>
@@ -327,6 +327,10 @@
   </si>
   <si>
     <t>cdRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -676,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I43"/>
+  <dimension ref="A2:I35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -933,31 +937,31 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G11" s="1">
-        <v>50104</v>
+        <v>50000</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -971,22 +975,22 @@
         <v>2</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G12" s="1">
-        <v>50000</v>
+        <v>50001</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -1000,80 +1004,80 @@
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G13" s="1">
-        <v>50001</v>
+        <v>50002</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1">
         <v>4</v>
       </c>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G14" s="1">
-        <v>50002</v>
+        <v>50006</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="1">
         <v>4</v>
       </c>
-      <c r="C15" s="1">
-        <v>2</v>
-      </c>
       <c r="D15" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G15" s="1">
-        <v>50003</v>
+        <v>50007</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -1087,120 +1091,120 @@
         <v>4</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G16" s="1">
-        <v>50006</v>
+        <v>50008</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17" s="1">
-        <v>50007</v>
+        <v>50012</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G18" s="1">
-        <v>50008</v>
+        <v>50013</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G19" s="1">
-        <v>50009</v>
+        <v>50014</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>62</v>
@@ -1212,7 +1216,7 @@
         <v>71</v>
       </c>
       <c r="G20" s="1">
-        <v>50012</v>
+        <v>50018</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>62</v>
@@ -1223,13 +1227,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>64</v>
@@ -1241,7 +1245,7 @@
         <v>72</v>
       </c>
       <c r="G21" s="1">
-        <v>50013</v>
+        <v>50019</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>64</v>
@@ -1252,13 +1256,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>66</v>
@@ -1270,7 +1274,7 @@
         <v>68</v>
       </c>
       <c r="G22" s="1">
-        <v>50014</v>
+        <v>50020</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>66</v>
@@ -1281,610 +1285,378 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C23" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G23" s="1">
-        <v>50015</v>
+        <v>50024</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1">
         <v>2</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G24" s="1">
-        <v>50018</v>
+        <v>50025</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G25" s="1">
-        <v>50019</v>
+        <v>50026</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G26" s="1">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G27" s="1">
-        <v>50021</v>
+        <v>50031</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G28" s="1">
-        <v>50024</v>
+        <v>50032</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C29" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G29" s="1">
-        <v>50025</v>
+        <v>50030</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C30" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G30" s="1">
-        <v>50026</v>
+        <v>50031</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C31" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G31" s="1">
-        <v>50027</v>
+        <v>50032</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C32" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="1">
-        <v>50030</v>
+        <v>67</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="4">
+        <v>50042</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C33" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" s="1">
-        <v>50031</v>
+        <v>76</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="4">
+        <v>50043</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C34" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G34" s="1">
-        <v>50032</v>
+        <v>76</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="4">
+        <v>50044</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G35" s="1">
-        <v>50033</v>
+        <v>76</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" s="4">
+        <v>50045</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
-        <v>1006</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G36" s="1">
-        <v>50030</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
-        <v>1006</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G37" s="1">
-        <v>50031</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
-        <v>1006</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G38" s="1">
-        <v>50032</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
-        <v>1006</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G39" s="1">
-        <v>50033</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
-        <v>1007</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="1">
-        <v>5</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40" s="4">
-        <v>50042</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
-        <v>1008</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="1">
-        <v>5</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G41" s="4">
-        <v>50043</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
-        <v>1009</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="1">
-        <v>2</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G42" s="4">
-        <v>50044</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
-        <v>1010</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="1">
-        <v>2</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G43" s="4">
-        <v>50045</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I43" s="4" t="s">
         <v>76</v>
       </c>
     </row>

--- a/Datas/TempCharacterCreateData.xlsx
+++ b/Datas/TempCharacterCreateData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="88">
   <si>
     <t>maxCharacterCount</t>
   </si>
@@ -249,10 +249,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>24,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>32,64</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -330,8 +326,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>24,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>23,0</t>
   </si>
 </sst>
 </file>
@@ -694,13 +689,13 @@
   <sheetData>
     <row r="2" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D2" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -737,7 +732,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>0</v>
@@ -749,7 +744,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>59</v>
@@ -766,28 +761,28 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="G5" s="1">
         <v>50100</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -795,28 +790,28 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G6" s="1">
         <v>50101</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -824,28 +819,28 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G7" s="1">
         <v>50101</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -853,28 +848,28 @@
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="F8" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G8" s="1">
         <v>50102</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -882,28 +877,28 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="1">
         <v>50103</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -911,28 +906,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" s="1">
         <v>50104</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -952,7 +947,7 @@
         <v>63</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G11" s="1">
         <v>50000</v>
@@ -981,7 +976,7 @@
         <v>65</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G12" s="1">
         <v>50001</v>
@@ -1007,10 +1002,10 @@
         <v>66</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G13" s="1">
         <v>50002</v>
@@ -1019,7 +1014,7 @@
         <v>66</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -1039,7 +1034,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" s="1">
         <v>50006</v>
@@ -1068,7 +1063,7 @@
         <v>65</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G15" s="1">
         <v>50007</v>
@@ -1094,10 +1089,10 @@
         <v>66</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G16" s="1">
         <v>50008</v>
@@ -1106,7 +1101,7 @@
         <v>66</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -1126,7 +1121,7 @@
         <v>63</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G17" s="1">
         <v>50012</v>
@@ -1155,7 +1150,7 @@
         <v>65</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G18" s="1">
         <v>50013</v>
@@ -1181,10 +1176,10 @@
         <v>66</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G19" s="1">
         <v>50014</v>
@@ -1193,7 +1188,7 @@
         <v>66</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1213,7 +1208,7 @@
         <v>63</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" s="1">
         <v>50018</v>
@@ -1242,7 +1237,7 @@
         <v>65</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G21" s="1">
         <v>50019</v>
@@ -1268,10 +1263,10 @@
         <v>66</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G22" s="1">
         <v>50020</v>
@@ -1280,7 +1275,7 @@
         <v>66</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -1300,7 +1295,7 @@
         <v>63</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G23" s="1">
         <v>50024</v>
@@ -1329,7 +1324,7 @@
         <v>65</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="1">
         <v>50025</v>
@@ -1355,10 +1350,10 @@
         <v>66</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G25" s="1">
         <v>50026</v>
@@ -1367,7 +1362,7 @@
         <v>66</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
@@ -1387,7 +1382,7 @@
         <v>63</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G26" s="1">
         <v>50030</v>
@@ -1416,7 +1411,7 @@
         <v>65</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G27" s="1">
         <v>50031</v>
@@ -1442,10 +1437,10 @@
         <v>66</v>
       </c>
       <c r="E28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G28" s="1">
         <v>50032</v>
@@ -1454,7 +1449,7 @@
         <v>66</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
@@ -1474,7 +1469,7 @@
         <v>63</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G29" s="1">
         <v>50030</v>
@@ -1503,7 +1498,7 @@
         <v>65</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G30" s="1">
         <v>50031</v>
@@ -1529,10 +1524,10 @@
         <v>66</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G31" s="1">
         <v>50032</v>
@@ -1541,7 +1536,7 @@
         <v>66</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
@@ -1555,10 +1550,10 @@
         <v>5</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>54</v>
@@ -1567,10 +1562,10 @@
         <v>50042</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -1584,10 +1579,10 @@
         <v>5</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>54</v>
@@ -1596,10 +1591,10 @@
         <v>50043</v>
       </c>
       <c r="H33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
@@ -1613,10 +1608,10 @@
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>54</v>
@@ -1625,10 +1620,10 @@
         <v>50044</v>
       </c>
       <c r="H34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
@@ -1642,10 +1637,10 @@
         <v>2</v>
       </c>
       <c r="D35" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>54</v>
@@ -1654,10 +1649,10 @@
         <v>50045</v>
       </c>
       <c r="H35" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
